--- a/artfynd/A 45685-2023 artfynd.xlsx
+++ b/artfynd/A 45685-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45685-2023 artfynd.xlsx
+++ b/artfynd/A 45685-2023 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>112587795</v>
       </c>
       <c r="B4" t="n">
-        <v>95394</v>
+        <v>95401</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>112588389</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45685-2023 artfynd.xlsx
+++ b/artfynd/A 45685-2023 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112587795</v>
+        <v>112588389</v>
       </c>
       <c r="B4" t="n">
-        <v>95401</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,21 +927,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,7 +958,7 @@
         <v>6729216</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112588389</v>
+        <v>112587795</v>
       </c>
       <c r="B5" t="n">
-        <v>78491</v>
+        <v>95401</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,7 +1071,7 @@
         <v>6729216</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
